--- a/ch_09/ch_09_solutions.xlsx
+++ b/ch_09/ch_09_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09_text_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C8C93-FB49-44B2-B745-DD3D0D488FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421C5059-4BD2-454D-8088-9229E61F6F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reviews" sheetId="1" r:id="rId1"/>
@@ -1628,9 +1628,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3008312</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>179097</xdr:rowOff>
+      <xdr:colOff>1508413</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1658,8 +1658,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="22717125"/>
-          <a:ext cx="7580312" cy="9489785"/>
+          <a:off x="0" y="30321250"/>
+          <a:ext cx="6080413" cy="7612063"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6091,7 +6091,7 @@
         <v>review_clean</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="285" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="str">
         <v>Wonderfull purchase. My neck pain from working at a laptop all day disappeared within a week of using this stand. The aluminum construction feels solid and the hinge holds any angle I set it to without drifting. Folds flat for travel.</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>wonderfull purchase. my neck pain from working at a laptop all day disappeared within a week of using this stand. the aluminum construction feels solid and the hinge holds any angle i set it to without drifting. folds flat for travel.</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="256.5" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="str">
         <v>The jacket is water resistant at best, not waterproof as advertised. During a steady rain I got damp underneath within about 20 minutes. Fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>the jacket is water resistant at best, not waterproof as advertised. during a steady rain i got damp underneath within about 20 minutes. fine for a quick dash to the car but not for extended outdoor use.</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="str">
         <v>Lovely candle. The scent throw is good — I can smell it from the next room when it's been burning for a while. My only complaint is that the jar gets quite hot so I have to be careful where I place it.</v>
       </c>
